--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1DB03D-D384-460D-B997-3F614484D108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90023081-B4AC-4228-AF01-39C402341462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13320" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="23" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -148,6 +148,81 @@
     <t>1.配車
 2.乗降場
 3.保安検査</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>refurbishment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>floorig bids</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改装</t>
+    <rPh sb="0" eb="2">
+      <t>カイソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>床材工事の見積もり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プリフィックス（セット）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>prix-fixe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>corkage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>持ち込み料</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>brewer,
+ledger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">,
+元帳
+</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -226,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -250,6 +325,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,7 +708,12 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>2</v>
       </c>
@@ -640,17 +723,27 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="72">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>2</v>
       </c>
@@ -660,7 +753,7 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="7"/>
       <c r="E11" s="2" t="s">
         <v>4</v>
       </c>
@@ -670,21 +763,31 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4">
+    <row r="13" spans="1:6" s="5" customFormat="1">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="E13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2"/>
+      <c r="B13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4">

--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90023081-B4AC-4228-AF01-39C402341462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386E13A8-1C43-48D2-9143-BE0CF7254251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="23" r:id="rId1"/>
     <sheet name="template" sheetId="20" r:id="rId2"/>
-    <sheet name="list" sheetId="2" r:id="rId3"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="39">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -223,6 +223,58 @@
 元帳
 </t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>paper Obstruction</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rear panel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背面パネル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペーパーオブストラクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>patio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中庭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>experiencing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直面している</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Concourse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央広場</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kettle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やかん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意思</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -614,6 +666,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="18.09765625" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -636,7 +689,7 @@
     </row>
     <row r="2" spans="1:6" ht="36">
       <c r="A2" s="4">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>13</v>
@@ -651,7 +704,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1"/>
       <c r="E3" s="2" t="s">
@@ -661,7 +714,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1"/>
       <c r="E4" s="2" t="s">
@@ -671,7 +724,7 @@
     </row>
     <row r="5" spans="1:6" ht="72">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -686,7 +739,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1"/>
       <c r="E6" s="2" t="s">
@@ -695,8 +748,8 @@
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1">
-      <c r="A7" s="8">
-        <v>6</v>
+      <c r="A7" s="4">
+        <v>37</v>
       </c>
       <c r="B7" s="9"/>
       <c r="E7" s="6" t="s">
@@ -706,7 +759,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -721,7 +774,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>17</v>
@@ -736,7 +789,7 @@
     </row>
     <row r="10" spans="1:6" ht="72">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>24</v>
@@ -751,7 +804,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B11" s="7"/>
       <c r="E11" s="2" t="s">
@@ -761,7 +814,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>21</v>
@@ -775,8 +828,8 @@
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" s="5" customFormat="1">
-      <c r="A13" s="8">
-        <v>12</v>
+      <c r="A13" s="4">
+        <v>43</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>22</v>
@@ -791,7 +844,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1"/>
       <c r="E14" s="2" t="s">
@@ -801,9 +854,14 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
@@ -811,9 +869,14 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
@@ -821,9 +884,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>4</v>
       </c>
@@ -831,7 +899,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1"/>
       <c r="E18" s="2" t="s">
@@ -841,7 +909,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1"/>
       <c r="E19" s="2" t="s">
@@ -851,9 +919,14 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>4</v>
       </c>
@@ -861,7 +934,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="4">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1"/>
       <c r="E21" s="2" t="s">
@@ -871,9 +944,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>4</v>
       </c>
@@ -881,9 +959,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>4</v>
       </c>
@@ -891,7 +974,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="4">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1"/>
       <c r="E24" s="2" t="s">
@@ -899,19 +982,19 @@
       </c>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="E25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="2"/>
+    <row r="25" spans="1:6" s="5" customFormat="1">
+      <c r="A25" s="8">
+        <v>55</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="E25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="4">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1"/>
       <c r="E26" s="2" t="s">
@@ -921,7 +1004,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="4">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1"/>
       <c r="E27" s="2" t="s">
@@ -931,7 +1014,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="4">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B28" s="1"/>
       <c r="E28" s="2" t="s">
@@ -941,7 +1024,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="4">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1"/>
       <c r="E29" s="2" t="s">
@@ -951,7 +1034,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1"/>
       <c r="E30" s="2" t="s">
@@ -961,7 +1044,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="4">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1"/>
       <c r="E31" s="2" t="s">
@@ -971,7 +1054,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B32" s="1"/>
       <c r="E32" s="2" t="s">
@@ -981,7 +1064,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1"/>
       <c r="E33" s="2" t="s">
@@ -991,7 +1074,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="4">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B34" s="1"/>
       <c r="E34" s="2" t="s">
@@ -1001,7 +1084,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="4">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B35" s="1"/>
       <c r="E35" s="2" t="s">
@@ -1011,7 +1094,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="4">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B36" s="1"/>
       <c r="E36" s="2" t="s">
@@ -1021,7 +1104,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="4">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B37" s="1"/>
       <c r="E37" s="2" t="s">
@@ -1031,7 +1114,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="4">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B38" s="1"/>
       <c r="E38" s="2" t="s">
@@ -1041,7 +1124,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="4">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B39" s="1"/>
       <c r="E39" s="2" t="s">
@@ -1051,7 +1134,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="4">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1"/>
       <c r="E40" s="2" t="s">
@@ -1061,7 +1144,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="4">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B41" s="1"/>
       <c r="E41" s="2" t="s">
@@ -1094,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1106,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
@@ -1117,7 +1200,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1"/>
       <c r="E2" s="2"/>
@@ -1125,7 +1208,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1"/>
       <c r="E3" s="2"/>
@@ -1133,7 +1216,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1"/>
       <c r="E4" s="2"/>
@@ -1141,7 +1224,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1"/>
       <c r="E5" s="2"/>
@@ -1149,7 +1232,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1"/>
       <c r="E6" s="2"/>
@@ -1157,7 +1240,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1"/>
       <c r="E7" s="2"/>
@@ -1165,7 +1248,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1"/>
       <c r="E8" s="2"/>
@@ -1173,7 +1256,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1"/>
       <c r="E9" s="2"/>
@@ -1181,7 +1264,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1"/>
       <c r="E10" s="2"/>
@@ -1189,7 +1272,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1"/>
       <c r="E11" s="2"/>
@@ -1197,7 +1280,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1"/>
       <c r="E12" s="2"/>
@@ -1205,7 +1288,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1"/>
       <c r="E13" s="2"/>
@@ -1213,7 +1296,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1"/>
       <c r="E14" s="2"/>
@@ -1221,7 +1304,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1"/>
       <c r="E15" s="2"/>
@@ -1229,7 +1312,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1"/>
       <c r="E16" s="2"/>
@@ -1237,7 +1320,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1"/>
       <c r="E17" s="2"/>
@@ -1245,7 +1328,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1"/>
       <c r="E18" s="2"/>
@@ -1253,7 +1336,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1"/>
       <c r="E19" s="2"/>
@@ -1261,7 +1344,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="4">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1"/>
       <c r="E20" s="2"/>
@@ -1269,7 +1352,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="4">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1"/>
       <c r="E21" s="2"/>
@@ -1277,7 +1360,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1"/>
       <c r="E22" s="2"/>
@@ -1285,7 +1368,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="4">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1"/>
       <c r="E23" s="2"/>
@@ -1293,7 +1376,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="4">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1"/>
       <c r="E24" s="2"/>
@@ -1301,7 +1384,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="4">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1"/>
       <c r="E25" s="2"/>
@@ -1309,7 +1392,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="4">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1"/>
       <c r="E26" s="2"/>
@@ -1317,7 +1400,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="4">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1"/>
       <c r="E27" s="2"/>
@@ -1325,7 +1408,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="4">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B28" s="1"/>
       <c r="E28" s="2"/>
@@ -1333,7 +1416,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="4">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1"/>
       <c r="E29" s="2"/>
@@ -1341,7 +1424,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1"/>
       <c r="E30" s="2"/>
@@ -1349,7 +1432,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="4">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1"/>
       <c r="E31" s="2"/>
@@ -1357,7 +1440,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B32" s="1"/>
       <c r="E32" s="2"/>
@@ -1365,7 +1448,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1"/>
       <c r="E33" s="2"/>
@@ -1373,7 +1456,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="4">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B34" s="1"/>
       <c r="E34" s="2"/>
@@ -1381,29 +1464,63 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="4">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B35" s="1"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="4">
+        <v>66</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="4">
+        <v>67</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="4">
+        <v>68</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="4">
+        <v>69</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="4">
+        <v>70</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1536C712-7FFF-4E4B-9871-E67CEB5EA6AB}">
-          <x14:formula1>
-            <xm:f>list!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D35</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB7A5466-31D6-47F4-B37A-875175599D26}">
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:F35</xm:sqref>
+          <xm:sqref>E2:F40</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386E13A8-1C43-48D2-9143-BE0CF7254251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC92C15-68B4-4427-8438-9207A3E5D4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -276,6 +276,44 @@
   <si>
     <t>意思</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sorting delay</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕分け（の）遅延</t>
+  </si>
+  <si>
+    <t>Foot traffic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>来店客数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>holds up to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大〜まで収容できる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spread across</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〜にわたって広がる / 〜全体に分散している</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>last</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>持続する</t>
   </si>
 </sst>
 </file>
@@ -722,7 +760,7 @@
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="72">
+    <row r="5" spans="1:6" ht="54">
       <c r="A5" s="4">
         <v>35</v>
       </c>
@@ -787,7 +825,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="72">
+    <row r="10" spans="1:6" ht="54">
       <c r="A10" s="4">
         <v>40</v>
       </c>
@@ -1016,7 +1054,6 @@
       <c r="A28" s="4">
         <v>58</v>
       </c>
-      <c r="B28" s="1"/>
       <c r="E28" s="2" t="s">
         <v>2</v>
       </c>
@@ -1026,7 +1063,12 @@
       <c r="A29" s="4">
         <v>59</v>
       </c>
-      <c r="B29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>2</v>
       </c>
@@ -1076,7 +1118,12 @@
       <c r="A34" s="4">
         <v>64</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>2</v>
       </c>
@@ -1096,7 +1143,12 @@
       <c r="A36" s="4">
         <v>66</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>4</v>
       </c>
@@ -1106,7 +1158,12 @@
       <c r="A37" s="4">
         <v>67</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>4</v>
       </c>
@@ -1116,7 +1173,12 @@
       <c r="A38" s="4">
         <v>68</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>4</v>
       </c>
@@ -1143,13 +1205,9 @@
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="4">
-        <v>71</v>
-      </c>
+      <c r="A41" s="4"/>
       <c r="B41" s="1"/>
-      <c r="E41" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="E41" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC92C15-68B4-4427-8438-9207A3E5D4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CAEBE3-763C-47E8-B550-2CF76CA40571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="23" r:id="rId1"/>
-    <sheet name="template" sheetId="20" r:id="rId2"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="02" sheetId="24" r:id="rId2"/>
+    <sheet name="03" sheetId="25" r:id="rId3"/>
+    <sheet name="template" sheetId="20" r:id="rId4"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -314,6 +316,10 @@
   </si>
   <si>
     <t>持続する</t>
+  </si>
+  <si>
+    <t>webinar</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1234,6 +1240,378 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35DB706-16B1-4F24-AB61-C83A760A4931}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
+        <v>62</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>63</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>64</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>65</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>66</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>67</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>68</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4">
+        <v>70</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8B67483D-7F46-4B32-8A6D-01D8F83A62FF}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F19</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D560B8B0-94B4-49FD-AD56-73DCDE7EDAC0}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>37</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>38</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>39</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0A1D509F-BED1-428D-9661-15292614C5FF}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F19</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -1586,7 +1964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CAEBE3-763C-47E8-B550-2CF76CA40571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19460D9B-29FE-4646-8A09-0D3C81DC7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="53">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -319,6 +319,18 @@
   </si>
   <si>
     <t>webinar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セミナー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rollout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>展開</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1299,6 +1311,9 @@
       <c r="B5" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1513,7 +1528,12 @@
       <c r="A8" s="4">
         <v>38</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>2</v>
       </c>

--- a/Toeic/Part3/ReviewWords.xlsx
+++ b/Toeic/Part3/ReviewWords.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\Part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19460D9B-29FE-4646-8A09-0D3C81DC7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A14A23-8DCF-487A-9ECD-5B7797C930F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="23" r:id="rId1"/>
     <sheet name="02" sheetId="24" r:id="rId2"/>
     <sheet name="03" sheetId="25" r:id="rId3"/>
-    <sheet name="template" sheetId="20" r:id="rId4"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="04" sheetId="26" r:id="rId4"/>
+    <sheet name="template" sheetId="20" r:id="rId5"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -333,12 +334,55 @@
     <t>展開</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>breakdown</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内訳</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明细</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配布資料</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Handout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>传单</t>
+  </si>
+  <si>
+    <t>gluten-free</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グルテンフリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>无麸质</t>
+  </si>
+  <si>
+    <t>Accommodate</t>
+  </si>
+  <si>
+    <t>対応する</t>
+  </si>
+  <si>
+    <t>配合</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +426,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -409,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -438,6 +489,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1632,6 +1684,227 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F8BF33-4D4E-4D1A-AE6B-9A7D7F730F12}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A2" s="4">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>37</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>38</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{956EC9F1-4CF3-430E-BBCA-A5A79F6B3D87}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F19</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -1984,7 +2257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18"/>
